--- a/Interview/Interviews_22-01-2025.xlsx
+++ b/Interview/Interviews_22-01-2025.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB0DF79F-3F86-4EF1-A18E-1C9355977E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="345" windowWidth="19875" windowHeight="7725"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interview_" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="calls" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
+    <sheet name="calls" sheetId="3" r:id="rId2"/>
+    <sheet name="2026" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Interview_!$A$1:$H$1</definedName>
@@ -20,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="91">
   <si>
     <t>date</t>
   </si>
@@ -826,11 +831,63 @@
   <si>
     <t>Requirement doesn’t suit my profile</t>
   </si>
+  <si>
+    <t>citiustech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not cracked </t>
+  </si>
+  <si>
+    <t>PERL</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>Data types in perl
+hash refernce and array reference
+length of array n hash
+upper case the hash vaues 
+remove dup in file and load to DB
+how to generte token ?</t>
+  </si>
+  <si>
+    <t>GLOBALTHOUGHTS</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. write data into file and count the length of each line in file 
+2. open the dire and read the dir find the files older thn 7 days and delete it .
+3. array of has of array.
+4. given the string find the prime numbers
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of joins
+constraint
+authe n autorization
+self join
+foreign keys
+union
+</t>
+  </si>
+  <si>
+    <t>comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how to read the file
+funtion within funtion </t>
+  </si>
+  <si>
+    <t>revise SQL</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -939,82 +996,88 @@
     <xf numFmtId="17" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,14 +1089,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1071,7 +1137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1143,7 +1209,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1316,7 +1382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1330,26 +1396,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1367,13 +1433,13 @@
       <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="11"/>
     </row>
     <row r="3" spans="1:8" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="17" t="s">
         <v>39</v>
       </c>
       <c r="B3" s="12" t="s">
@@ -1391,7 +1457,7 @@
       <c r="F3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1414,7 +1480,7 @@
       <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="20"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1435,7 +1501,7 @@
       <c r="F5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="21"/>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -1456,10 +1522,10 @@
       <c r="F6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="21"/>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="150" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -1477,7 +1543,7 @@
       <c r="F7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="21"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -1498,7 +1564,7 @@
       <c r="F8" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:8" ht="315" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -1519,10 +1585,10 @@
       <c r="F9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="21"/>
+      <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -1540,189 +1606,175 @@
       <c r="F10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" ht="180" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="19">
         <v>1</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="21"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="345" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:8" ht="184.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
       <c r="E13" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:8" ht="225" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="24" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
         <v>80</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="30" t="s">
+      <c r="F14" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
+      <c r="A15" s="26">
         <v>45673</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
         <v>50</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="33">
+      <c r="A16" s="27">
         <v>45673</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
         <v>50</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="32"/>
-    </row>
-    <row r="17" spans="1:7" ht="285" x14ac:dyDescent="0.25">
-      <c r="A17" s="33">
+    </row>
+    <row r="17" spans="1:6" ht="285" x14ac:dyDescent="0.25">
+      <c r="A17" s="27">
         <v>45677</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="29" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="32"/>
-    </row>
-    <row r="18" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="34" t="s">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G18" s="32"/>
-    </row>
-    <row r="19" spans="1:7" ht="345" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="345" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="14" t="s">
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="32"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1967,14 +2019,100 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15"/>
+      <c r="G1" s="32"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="27">
+        <v>46083</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="18">
+        <v>0</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="30" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>